--- a/output/pdf_financials_xlsx/VUX.xlsx
+++ b/output/pdf_financials_xlsx/VUX.xlsx
@@ -1428,10 +1428,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.038956</v>
+        <v>-5.334666</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.188239</v>
+        <v>-32.322281</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-4.488719</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.647855</v>
+        <v>-2.647855</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>16.067021</v>
+        <v>-16.067021</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-2.147913</v>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.647855</v>
+        <v>-2.647855</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>16.067021</v>
+        <v>-16.067021</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-2.147913</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-66.196375</v>
+        <v>66.196375</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-15.301925</v>
+        <v>15.301925</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>14.31942</v>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.449897294599434</v>
+        <v>198.5501027054006</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1.15801900430999</v>
+        <v>198.84198099569</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>191.7595477796964</v>
@@ -6197,19 +6197,19 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>2.393666</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>4.025809</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>5.35578</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>6.69019</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>6.397908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -45965,13 +45965,13 @@
         </is>
       </c>
       <c r="F427" s="5" t="n">
-        <v>2.647855</v>
+        <v>-2.647855</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>16.067021</v>
+        <v>-16.067021</v>
       </c>
       <c r="H427" s="5" t="n">
-        <v>2.340806</v>
+        <v>-2.340806</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VUX.xlsx
+++ b/output/pdf_financials_xlsx/VUX.xlsx
@@ -1096,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.040824</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023599</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004908</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.686811</v>
+        <v>2.727635</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.25526</v>
+        <v>16.278859</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.340806</v>
+        <v>2.345714</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.854452</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.686811</v>
+        <v>2.727635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>16.25526</v>
+        <v>16.278859</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.780368</v>
+        <v>3.785276</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.459557</v>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.189697</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.402885</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.395545</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.577441</v>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.189697</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.402885</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.395545</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.577441</v>
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.270531</v>
+        <v>0.080834</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.679838</v>
+        <v>0.276953</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.522343</v>
+        <v>0.126798</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.022064</v>
@@ -6197,19 +6197,19 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>2.393666</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>4.025809</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>5.35578</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>6.69019</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>6.397908</v>
       </c>
     </row>
     <row r="101">
@@ -21549,7 +21549,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -45683,7 +45683,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">

--- a/output/pdf_financials_xlsx/VUX.xlsx
+++ b/output/pdf_financials_xlsx/VUX.xlsx
@@ -1428,10 +1428,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-5.334666</v>
+        <v>0.038956</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-32.322281</v>
+        <v>0.188239</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-4.488719</v>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>198.5501027054006</v>
+        <v>1.449897294599434</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>198.84198099569</v>
+        <v>1.15801900430999</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>191.7595477796964</v>
@@ -6252,16 +6252,16 @@
         <v>-1.340033</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0.534635</v>
+        <v>0.371866</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.193578</v>
+        <v>-0.048706</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>-1.486572</v>
+        <v>-1.320894</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0.949834</v>
+        <v>0.822782</v>
       </c>
     </row>
     <row r="102">
@@ -6512,16 +6512,16 @@
         <v>-1.501976</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>1.877408</v>
+        <v>1.714639</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>3.999644</v>
+        <v>3.75736</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-4.699302</v>
+        <v>-4.533624</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.098312</v>
+        <v>-0.225364</v>
       </c>
     </row>
     <row r="107">
@@ -25873,7 +25873,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27567,7 +27571,11 @@
           <t>Deferred income tax (recovery) 15</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -28627,7 +28635,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -30292,7 +30304,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -33680,7 +33696,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -45863,7 +45883,11 @@
           <t>Deferred income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -46498,7 +46522,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
